--- a/Emissao.XLSX
+++ b/Emissao.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="131">
   <si>
     <t>E90R</t>
   </si>
@@ -22,67 +22,292 @@
     <t>CHECK_IN</t>
   </si>
   <si>
+    <t>LUANN M ADUBOS E FERTILIZANTES LTDA</t>
+  </si>
+  <si>
+    <t>1010003382</t>
+  </si>
+  <si>
+    <t>18.04.10+0,05B+0,2ZN MT</t>
+  </si>
+  <si>
+    <t>SACARIA 50KG</t>
+  </si>
+  <si>
+    <t>AUGUSTO DIVINO DE SOUZA SILVA</t>
+  </si>
+  <si>
+    <t>NDW1F14</t>
+  </si>
+  <si>
+    <t>FOB</t>
+  </si>
+  <si>
+    <t>2149047</t>
+  </si>
+  <si>
+    <t>281050</t>
+  </si>
+  <si>
+    <t>1230477</t>
+  </si>
+  <si>
+    <t>80593416</t>
+  </si>
+  <si>
+    <t>HENRIQUE DIAS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>MAZ1G22</t>
+  </si>
+  <si>
+    <t>1230478</t>
+  </si>
+  <si>
+    <t>80593421</t>
+  </si>
+  <si>
     <t>CASA AGRI HELIO MORENO LTDA</t>
   </si>
   <si>
-    <t>1010003554</t>
-  </si>
-  <si>
-    <t>20.00.20 C+ NBPT</t>
-  </si>
-  <si>
-    <t>SACARIA 50KG</t>
-  </si>
-  <si>
-    <t>SAULO CARLOS DA FONSECA</t>
-  </si>
-  <si>
-    <t>SGF8A32</t>
-  </si>
-  <si>
-    <t>FOB</t>
-  </si>
-  <si>
-    <t>2149296</t>
-  </si>
-  <si>
-    <t>281752</t>
-  </si>
-  <si>
-    <t>1229950</t>
-  </si>
-  <si>
-    <t>80592670</t>
-  </si>
-  <si>
-    <t>LUANN M ADUBOS E FERTILIZANTES LTDA</t>
-  </si>
-  <si>
     <t>1010002694</t>
   </si>
   <si>
     <t>18.04.17 NBPT</t>
   </si>
   <si>
-    <t>JOAO VICTOR MACHADO SILVA</t>
-  </si>
-  <si>
-    <t>MRX8J72</t>
-  </si>
-  <si>
-    <t>2149047</t>
-  </si>
-  <si>
-    <t>281940</t>
-  </si>
-  <si>
-    <t>1229952</t>
-  </si>
-  <si>
-    <t>80592687</t>
-  </si>
-  <si>
-    <t>AGROFERTI FERTILIZANTES LTDA</t>
+    <t>EDIONIS FERREIRA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>TOF6D10</t>
+  </si>
+  <si>
+    <t>2148423</t>
+  </si>
+  <si>
+    <t>282039</t>
+  </si>
+  <si>
+    <t>1230479</t>
+  </si>
+  <si>
+    <t>80593401</t>
+  </si>
+  <si>
+    <t>VINICIUS BURGARELLI COSTA</t>
+  </si>
+  <si>
+    <t>1010002488</t>
+  </si>
+  <si>
+    <t>26.00.26 BYSLB SEG</t>
+  </si>
+  <si>
+    <t>EDSON CESAR BARBOSA TRIVILIM</t>
+  </si>
+  <si>
+    <t>MPU6B44</t>
+  </si>
+  <si>
+    <t>2154035</t>
+  </si>
+  <si>
+    <t>280924</t>
+  </si>
+  <si>
+    <t>1230501</t>
+  </si>
+  <si>
+    <t>80593397</t>
+  </si>
+  <si>
+    <t>H2N ABREU COMERCIO DE PRODUTOS AGRI</t>
+  </si>
+  <si>
+    <t>1010001181</t>
+  </si>
+  <si>
+    <t>33.00.00 NBPT</t>
+  </si>
+  <si>
+    <t>ATILA CORREA</t>
+  </si>
+  <si>
+    <t>GKW0E90</t>
+  </si>
+  <si>
+    <t>2149297</t>
+  </si>
+  <si>
+    <t>280068</t>
+  </si>
+  <si>
+    <t>1230502</t>
+  </si>
+  <si>
+    <t>80593424</t>
+  </si>
+  <si>
+    <t>1010003557</t>
+  </si>
+  <si>
+    <t>18.04.17 C+ NBPT</t>
+  </si>
+  <si>
+    <t>RENATO RODRIGUES GONÇALVES</t>
+  </si>
+  <si>
+    <t>OCV3I73</t>
+  </si>
+  <si>
+    <t>2149295</t>
+  </si>
+  <si>
+    <t>280066</t>
+  </si>
+  <si>
+    <t>1230511</t>
+  </si>
+  <si>
+    <t>80593461</t>
+  </si>
+  <si>
+    <t>MP COMERCIAL AGRICOLA LTDA</t>
+  </si>
+  <si>
+    <t>1010003163</t>
+  </si>
+  <si>
+    <t>03.17.00 C+</t>
+  </si>
+  <si>
+    <t>ELIAS COELHO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>PPR9A77</t>
+  </si>
+  <si>
+    <t>2155239</t>
+  </si>
+  <si>
+    <t>282989</t>
+  </si>
+  <si>
+    <t>1230514</t>
+  </si>
+  <si>
+    <t>80593480</t>
+  </si>
+  <si>
+    <t>COOPERATIVA AGRARIA DOS CAFEICULTOR</t>
+  </si>
+  <si>
+    <t>1010002973</t>
+  </si>
+  <si>
+    <t>08.40.08+0,1B+0,2ZN C HMC</t>
+  </si>
+  <si>
+    <t>BIG BAG 1000KG</t>
+  </si>
+  <si>
+    <t>LUIZ ACERBI</t>
+  </si>
+  <si>
+    <t>JLX3480</t>
+  </si>
+  <si>
+    <t>2154198</t>
+  </si>
+  <si>
+    <t>283010</t>
+  </si>
+  <si>
+    <t>1230555</t>
+  </si>
+  <si>
+    <t>80593527</t>
+  </si>
+  <si>
+    <t>1010000036</t>
+  </si>
+  <si>
+    <t>MAP 11-52-00</t>
+  </si>
+  <si>
+    <t>FABIO DE SOUZA CRUZ</t>
+  </si>
+  <si>
+    <t>LXA8250</t>
+  </si>
+  <si>
+    <t>2154486</t>
+  </si>
+  <si>
+    <t>282855</t>
+  </si>
+  <si>
+    <t>1230577</t>
+  </si>
+  <si>
+    <t>80593597</t>
+  </si>
+  <si>
+    <t>CULTIVAR INSUMOS AGRICOLAS LTDA</t>
+  </si>
+  <si>
+    <t>WALACE MARTINELLI</t>
+  </si>
+  <si>
+    <t>KSR6C49</t>
+  </si>
+  <si>
+    <t>2153982</t>
+  </si>
+  <si>
+    <t>279307</t>
+  </si>
+  <si>
+    <t>1230579</t>
+  </si>
+  <si>
+    <t>80593588</t>
+  </si>
+  <si>
+    <t>ROGERIO DINIZ DA SILVA</t>
+  </si>
+  <si>
+    <t>MSQ9I16</t>
+  </si>
+  <si>
+    <t>281299</t>
+  </si>
+  <si>
+    <t>1230600</t>
+  </si>
+  <si>
+    <t>80593591</t>
+  </si>
+  <si>
+    <t>281350</t>
+  </si>
+  <si>
+    <t>1230602</t>
+  </si>
+  <si>
+    <t>80593593</t>
+  </si>
+  <si>
+    <t>283019</t>
+  </si>
+  <si>
+    <t>1230603</t>
+  </si>
+  <si>
+    <t>80593594</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
   <si>
     <t>1010001068</t>
@@ -94,112 +319,37 @@
     <t>SACARIA 25KG</t>
   </si>
   <si>
-    <t>MARCO AURELIO ROCHA</t>
-  </si>
-  <si>
-    <t>KEQ3F93</t>
-  </si>
-  <si>
-    <t>2154242</t>
-  </si>
-  <si>
-    <t>280965</t>
-  </si>
-  <si>
-    <t>1229957</t>
-  </si>
-  <si>
-    <t>80592722</t>
-  </si>
-  <si>
-    <t>H2N ABREU COMERCIO DE PRODUTOS AGRI</t>
-  </si>
-  <si>
-    <t>1010003557</t>
-  </si>
-  <si>
-    <t>18.04.17 C+ NBPT</t>
-  </si>
-  <si>
-    <t>HUDSON WOLFFGRAM</t>
-  </si>
-  <si>
-    <t>ODM7H75</t>
-  </si>
-  <si>
-    <t>2149295</t>
-  </si>
-  <si>
-    <t>281119</t>
-  </si>
-  <si>
-    <t>1230021</t>
-  </si>
-  <si>
-    <t>80592692</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>ROGERIO DINIZ DA SILVA</t>
-  </si>
-  <si>
-    <t>MSQ9I16</t>
-  </si>
-  <si>
-    <t>2148423</t>
-  </si>
-  <si>
-    <t>281756</t>
-  </si>
-  <si>
-    <t>1229916</t>
-  </si>
-  <si>
-    <t>80592637</t>
-  </si>
-  <si>
-    <t>1010001404</t>
-  </si>
-  <si>
-    <t>20.00.20 NBPT</t>
-  </si>
-  <si>
-    <t>2151516</t>
-  </si>
-  <si>
-    <t>281302</t>
-  </si>
-  <si>
-    <t>1229949</t>
-  </si>
-  <si>
-    <t>80592671</t>
-  </si>
-  <si>
-    <t>281762</t>
-  </si>
-  <si>
-    <t>1229951</t>
-  </si>
-  <si>
-    <t>80592673</t>
-  </si>
-  <si>
-    <t>ODM7H15</t>
-  </si>
-  <si>
     <t>2154303</t>
   </si>
   <si>
-    <t>281118</t>
+    <t>281876</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>80592691</t>
+    <t>80593459</t>
+  </si>
+  <si>
+    <t>282891</t>
+  </si>
+  <si>
+    <t>80593460</t>
+  </si>
+  <si>
+    <t>JOAO MARCOS SILVEIRA VIEIRA</t>
+  </si>
+  <si>
+    <t>SFT0C40</t>
+  </si>
+  <si>
+    <t>2151650</t>
+  </si>
+  <si>
+    <t>282044</t>
+  </si>
+  <si>
+    <t>80593479</t>
   </si>
   <si>
     <t>Planta</t>
@@ -378,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="8" customWidth="1"/>
@@ -388,10 +538,10 @@
     <col min="5" max="5" bestFit="1" width="17" customWidth="1"/>
     <col min="6" max="6" bestFit="1" width="37" customWidth="1"/>
     <col min="7" max="7" bestFit="1" width="20" customWidth="1"/>
-    <col min="8" max="8" bestFit="1" width="22" customWidth="1"/>
+    <col min="8" max="8" bestFit="1" width="27" customWidth="1"/>
     <col min="9" max="9" bestFit="1" width="20" customWidth="1"/>
-    <col min="10" max="10" bestFit="1" width="8" customWidth="1"/>
-    <col min="11" max="11" bestFit="1" width="27" customWidth="1"/>
+    <col min="10" max="10" bestFit="1" width="18" customWidth="1"/>
+    <col min="11" max="11" bestFit="1" width="31" customWidth="1"/>
     <col min="12" max="12" bestFit="1" width="9" customWidth="1"/>
     <col min="13" max="13" bestFit="1" width="5" customWidth="1"/>
     <col min="14" max="14" bestFit="1" width="17" customWidth="1"/>
@@ -403,58 +553,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>113</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>65</v>
+        <v>115</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>67</v>
+        <v>117</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>68</v>
+        <v>118</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="J1" s="9" t="s">
-        <v>72</v>
+        <v>121</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>79</v>
+        <v>129</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>80</v>
+        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -468,10 +618,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E2" s="3">
-        <v>0.35033564814815</v>
+        <v>0.32697916666667</v>
       </c>
       <c r="F2" t="s">
         <v>3</v>
@@ -486,7 +636,7 @@
         <v>6</v>
       </c>
       <c r="J2" s="4">
-        <v>9.000</v>
+        <v>32.000</v>
       </c>
       <c r="K2" t="s">
         <v>7</v>
@@ -498,7 +648,7 @@
         <v>9</v>
       </c>
       <c r="N2" s="4">
-        <v>9.000</v>
+        <v>32.000</v>
       </c>
       <c r="O2" t="s">
         <v>10</v>
@@ -524,19 +674,19 @@
         <v>2</v>
       </c>
       <c r="D3" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E3" s="3">
-        <v>0.36307870370370</v>
+        <v>0.32853009259259</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I3" t="s">
         <v>6</v>
@@ -545,10 +695,10 @@
         <v>19.000</v>
       </c>
       <c r="K3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M3" t="s">
         <v>9</v>
@@ -557,16 +707,16 @@
         <v>19.000</v>
       </c>
       <c r="O3" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="P3" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="Q3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="R3" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -580,49 +730,49 @@
         <v>2</v>
       </c>
       <c r="D4" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E4" s="3">
-        <v>0.38578703703704</v>
+        <v>0.33020833333333</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="J4" s="4">
-        <v>14.000</v>
+        <v>19.000</v>
       </c>
       <c r="K4" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="L4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="M4" t="s">
         <v>9</v>
       </c>
       <c r="N4" s="4">
-        <v>14.000</v>
+        <v>19.000</v>
       </c>
       <c r="O4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="P4" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="Q4" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="R4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -636,49 +786,49 @@
         <v>2</v>
       </c>
       <c r="D5" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E5" s="3">
-        <v>0.40572916666667</v>
+        <v>0.33174768518519</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="I5" t="s">
         <v>6</v>
       </c>
       <c r="J5" s="4">
-        <v>6.000</v>
+        <v>32.000</v>
       </c>
       <c r="K5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="L5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="M5" t="s">
         <v>9</v>
       </c>
       <c r="N5" s="4">
-        <v>6.000</v>
+        <v>32.000</v>
       </c>
       <c r="O5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="P5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="Q5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="R5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -686,55 +836,55 @@
         <v>0</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="C6" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E6" s="3">
-        <v>0.33120370370370</v>
+        <v>0.33276620370370</v>
       </c>
       <c r="F6" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="I6" t="s">
         <v>6</v>
       </c>
       <c r="J6" s="4">
-        <v>19.000</v>
+        <v>15.000</v>
       </c>
       <c r="K6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M6" t="s">
         <v>9</v>
       </c>
       <c r="N6" s="4">
-        <v>0.000</v>
+        <v>15.000</v>
       </c>
       <c r="O6" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="P6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Q6" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="R6" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -742,55 +892,55 @@
         <v>0</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="C7" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E7" s="3">
-        <v>0.34835648148148</v>
+        <v>0.35784722222222</v>
       </c>
       <c r="F7" t="s">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H7" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="I7" t="s">
         <v>6</v>
       </c>
       <c r="J7" s="4">
-        <v>5.000</v>
+        <v>12.000</v>
       </c>
       <c r="K7" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="L7" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="M7" t="s">
         <v>9</v>
       </c>
       <c r="N7" s="4">
-        <v>0.000</v>
+        <v>12.000</v>
       </c>
       <c r="O7" t="s">
+        <v>49</v>
+      </c>
+      <c r="P7" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q7" t="s">
         <v>51</v>
       </c>
-      <c r="P7" t="s">
+      <c r="R7" t="s">
         <v>52</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>53</v>
-      </c>
-      <c r="R7" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -798,55 +948,55 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="C8" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E8" s="3">
-        <v>0.35182870370370</v>
+        <v>0.36076388888889</v>
       </c>
       <c r="F8" t="s">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="G8" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H8" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I8" t="s">
         <v>6</v>
       </c>
       <c r="J8" s="4">
-        <v>5.000</v>
+        <v>14.000</v>
       </c>
       <c r="K8" t="s">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="L8" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="M8" t="s">
         <v>9</v>
       </c>
       <c r="N8" s="4">
-        <v>0.000</v>
+        <v>14.000</v>
       </c>
       <c r="O8" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="P8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="Q8" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="R8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -854,107 +1004,555 @@
         <v>0</v>
       </c>
       <c r="B9" t="s">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="C9" t="s">
         <v>2</v>
       </c>
       <c r="D9" s="2">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="E9" s="3">
-        <v>0.37762731481481</v>
+        <v>0.38931712962963</v>
       </c>
       <c r="F9" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="G9" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="H9" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="I9" t="s">
-        <v>26</v>
+        <v>65</v>
       </c>
       <c r="J9" s="4">
-        <v>0.000</v>
+        <v>26.000</v>
       </c>
       <c r="K9" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="L9" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="M9" t="s">
         <v>9</v>
       </c>
       <c r="N9" s="4">
+        <v>26.000</v>
+      </c>
+      <c r="O9" t="s">
+        <v>68</v>
+      </c>
+      <c r="P9" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>70</v>
+      </c>
+      <c r="R9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2">
+        <v>46241</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0.41789351851852</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" t="s">
+        <v>73</v>
+      </c>
+      <c r="I10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J10" s="4">
+        <v>16.000</v>
+      </c>
+      <c r="K10" t="s">
+        <v>74</v>
+      </c>
+      <c r="L10" t="s">
+        <v>75</v>
+      </c>
+      <c r="M10" t="s">
+        <v>9</v>
+      </c>
+      <c r="N10" s="4">
+        <v>16.000</v>
+      </c>
+      <c r="O10" t="s">
+        <v>76</v>
+      </c>
+      <c r="P10" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>78</v>
+      </c>
+      <c r="R10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2">
+        <v>46241</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0.42024305555556</v>
+      </c>
+      <c r="F11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I11" t="s">
+        <v>6</v>
+      </c>
+      <c r="J11" s="4">
+        <v>15.000</v>
+      </c>
+      <c r="K11" t="s">
+        <v>81</v>
+      </c>
+      <c r="L11" t="s">
+        <v>82</v>
+      </c>
+      <c r="M11" t="s">
+        <v>9</v>
+      </c>
+      <c r="N11" s="4">
+        <v>15.000</v>
+      </c>
+      <c r="O11" t="s">
+        <v>83</v>
+      </c>
+      <c r="P11" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>85</v>
+      </c>
+      <c r="R11" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2">
+        <v>46241</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0.42111111111111</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" t="s">
+        <v>6</v>
+      </c>
+      <c r="J12" s="4">
+        <v>6.000</v>
+      </c>
+      <c r="K12" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" t="s">
+        <v>9</v>
+      </c>
+      <c r="N12" s="4">
+        <v>6.000</v>
+      </c>
+      <c r="O12" t="s">
+        <v>23</v>
+      </c>
+      <c r="P12" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>90</v>
+      </c>
+      <c r="R12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2">
+        <v>46241</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.42248842592593</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" t="s">
+        <v>6</v>
+      </c>
+      <c r="J13" s="4">
+        <v>5.000</v>
+      </c>
+      <c r="K13" t="s">
+        <v>87</v>
+      </c>
+      <c r="L13" t="s">
+        <v>88</v>
+      </c>
+      <c r="M13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N13" s="4">
+        <v>5.000</v>
+      </c>
+      <c r="O13" t="s">
+        <v>23</v>
+      </c>
+      <c r="P13" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>93</v>
+      </c>
+      <c r="R13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="2">
+        <v>46241</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.42381944444444</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" t="s">
+        <v>6</v>
+      </c>
+      <c r="J14" s="4">
+        <v>8.000</v>
+      </c>
+      <c r="K14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L14" t="s">
+        <v>88</v>
+      </c>
+      <c r="M14" t="s">
+        <v>9</v>
+      </c>
+      <c r="N14" s="4">
+        <v>8.000</v>
+      </c>
+      <c r="O14" t="s">
+        <v>23</v>
+      </c>
+      <c r="P14" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>96</v>
+      </c>
+      <c r="R14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2">
+        <v>46241</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.36270833333333</v>
+      </c>
+      <c r="F15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" t="s">
+        <v>99</v>
+      </c>
+      <c r="H15" t="s">
+        <v>100</v>
+      </c>
+      <c r="I15" t="s">
+        <v>101</v>
+      </c>
+      <c r="J15" s="4">
         <v>0.000</v>
       </c>
-      <c r="O9" t="s">
-        <v>59</v>
-      </c>
-      <c r="P9" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>61</v>
-      </c>
-      <c r="R9" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="J10" s="8">
-        <v>77.000</v>
-      </c>
-      <c r="K10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="L10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="M10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="N10" s="8">
-        <v>48.000</v>
-      </c>
-      <c r="O10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="P10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="R10" s="5" t="s">
-        <v>61</v>
+      <c r="K15" t="s">
+        <v>47</v>
+      </c>
+      <c r="L15" t="s">
+        <v>48</v>
+      </c>
+      <c r="M15" t="s">
+        <v>9</v>
+      </c>
+      <c r="N15" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="O15" t="s">
+        <v>102</v>
+      </c>
+      <c r="P15" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>104</v>
+      </c>
+      <c r="R15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="2">
+        <v>46241</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.36471064814815</v>
+      </c>
+      <c r="F16" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" t="s">
+        <v>99</v>
+      </c>
+      <c r="H16" t="s">
+        <v>100</v>
+      </c>
+      <c r="I16" t="s">
+        <v>101</v>
+      </c>
+      <c r="J16" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="K16" t="s">
+        <v>47</v>
+      </c>
+      <c r="L16" t="s">
+        <v>48</v>
+      </c>
+      <c r="M16" t="s">
+        <v>9</v>
+      </c>
+      <c r="N16" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="O16" t="s">
+        <v>102</v>
+      </c>
+      <c r="P16" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>104</v>
+      </c>
+      <c r="R16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="2">
+        <v>46241</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0.36662037037037</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" t="s">
+        <v>100</v>
+      </c>
+      <c r="I17" t="s">
+        <v>101</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="K17" t="s">
+        <v>108</v>
+      </c>
+      <c r="L17" t="s">
+        <v>109</v>
+      </c>
+      <c r="M17" t="s">
+        <v>9</v>
+      </c>
+      <c r="N17" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="O17" t="s">
+        <v>110</v>
+      </c>
+      <c r="P17" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>104</v>
+      </c>
+      <c r="R17" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="6"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="J18" s="8">
+        <v>219.000</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="N18" s="8">
+        <v>219.000</v>
+      </c>
+      <c r="O18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="P18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q18" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="R18" s="5" t="s">
+        <v>104</v>
       </c>
     </row>
   </sheetData>

--- a/Emissao.XLSX
+++ b/Emissao.XLSX
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="189">
   <si>
     <t>E90R</t>
   </si>
@@ -22,334 +22,508 @@
     <t>CHECK_IN</t>
   </si>
   <si>
+    <t>FERT MAIS AGROPECUARIA LTDA</t>
+  </si>
+  <si>
+    <t>1010001068</t>
+  </si>
+  <si>
+    <t>KCL 00-00-61 SLB</t>
+  </si>
+  <si>
+    <t>SACARIA 50KG</t>
+  </si>
+  <si>
+    <t>PAULENE BISPO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>PPI7E63</t>
+  </si>
+  <si>
+    <t>FOB</t>
+  </si>
+  <si>
+    <t>2154217</t>
+  </si>
+  <si>
+    <t>282678</t>
+  </si>
+  <si>
+    <t>1233188</t>
+  </si>
+  <si>
+    <t>80599142</t>
+  </si>
+  <si>
+    <t>1010002488</t>
+  </si>
+  <si>
+    <t>26.00.26 BYSLB</t>
+  </si>
+  <si>
+    <t>SACARIA 25KG</t>
+  </si>
+  <si>
+    <t>2155377</t>
+  </si>
+  <si>
+    <t>282679</t>
+  </si>
+  <si>
+    <t>1233189</t>
+  </si>
+  <si>
+    <t>80599141</t>
+  </si>
+  <si>
     <t>LUANN M ADUBOS E FERTILIZANTES LTDA</t>
   </si>
   <si>
-    <t>1010003382</t>
-  </si>
-  <si>
-    <t>18.04.10+0,05B+0,2ZN MT</t>
-  </si>
-  <si>
-    <t>SACARIA 50KG</t>
-  </si>
-  <si>
-    <t>AUGUSTO DIVINO DE SOUZA SILVA</t>
-  </si>
-  <si>
-    <t>NDW1F14</t>
-  </si>
-  <si>
-    <t>FOB</t>
+    <t>1010002694</t>
+  </si>
+  <si>
+    <t>18.04.17 NBPT</t>
+  </si>
+  <si>
+    <t>JOSUE FERNANDES MOREIRA</t>
+  </si>
+  <si>
+    <t>MRV2A99</t>
   </si>
   <si>
     <t>2149047</t>
   </si>
   <si>
-    <t>281050</t>
-  </si>
-  <si>
-    <t>1230477</t>
-  </si>
-  <si>
-    <t>80593416</t>
-  </si>
-  <si>
-    <t>HENRIQUE DIAS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>MAZ1G22</t>
-  </si>
-  <si>
-    <t>1230478</t>
-  </si>
-  <si>
-    <t>80593421</t>
+    <t>284222</t>
+  </si>
+  <si>
+    <t>1233194</t>
+  </si>
+  <si>
+    <t>80599173</t>
+  </si>
+  <si>
+    <t>1010000943</t>
+  </si>
+  <si>
+    <t>UREIA 46-00-00</t>
+  </si>
+  <si>
+    <t>2152290</t>
+  </si>
+  <si>
+    <t>284215</t>
+  </si>
+  <si>
+    <t>1233196</t>
+  </si>
+  <si>
+    <t>80599174</t>
+  </si>
+  <si>
+    <t>1010002701</t>
+  </si>
+  <si>
+    <t>18.04.17</t>
+  </si>
+  <si>
+    <t>284208</t>
+  </si>
+  <si>
+    <t>1233199</t>
+  </si>
+  <si>
+    <t>80599175</t>
+  </si>
+  <si>
+    <t>APOIO DIST AGRI LTDA</t>
+  </si>
+  <si>
+    <t>VANDERLEI SCHWANZ</t>
+  </si>
+  <si>
+    <t>MRA1933</t>
+  </si>
+  <si>
+    <t>2155397</t>
+  </si>
+  <si>
+    <t>284000</t>
+  </si>
+  <si>
+    <t>1233212</t>
+  </si>
+  <si>
+    <t>80599191</t>
+  </si>
+  <si>
+    <t>2154686</t>
+  </si>
+  <si>
+    <t>283999</t>
+  </si>
+  <si>
+    <t>1233213</t>
+  </si>
+  <si>
+    <t>80599190</t>
+  </si>
+  <si>
+    <t>AGROFERTI FERTILIZANTES LTDA</t>
+  </si>
+  <si>
+    <t>SEBASTIAO RIBEIRO NETO</t>
+  </si>
+  <si>
+    <t>KHM1A14</t>
+  </si>
+  <si>
+    <t>2155606</t>
+  </si>
+  <si>
+    <t>283196</t>
+  </si>
+  <si>
+    <t>1233214</t>
+  </si>
+  <si>
+    <t>80599197</t>
+  </si>
+  <si>
+    <t>283195</t>
+  </si>
+  <si>
+    <t>1233215</t>
+  </si>
+  <si>
+    <t>80599198</t>
+  </si>
+  <si>
+    <t>PAIOL COM AGROP LTDA</t>
+  </si>
+  <si>
+    <t>1010000036</t>
+  </si>
+  <si>
+    <t>MAP 11-52-00</t>
+  </si>
+  <si>
+    <t>Ronaldo marques pereira</t>
+  </si>
+  <si>
+    <t>AKU8I50</t>
+  </si>
+  <si>
+    <t>2155673</t>
+  </si>
+  <si>
+    <t>283967</t>
+  </si>
+  <si>
+    <t>1233216</t>
+  </si>
+  <si>
+    <t>80599194</t>
+  </si>
+  <si>
+    <t>AGROZAN AGROP ZANOTELLI LTDA</t>
+  </si>
+  <si>
+    <t>EVERSON TOREZANI</t>
+  </si>
+  <si>
+    <t>ODL4783</t>
+  </si>
+  <si>
+    <t>2155511</t>
+  </si>
+  <si>
+    <t>282595</t>
+  </si>
+  <si>
+    <t>1233218</t>
+  </si>
+  <si>
+    <t>80599215</t>
+  </si>
+  <si>
+    <t>H2N ABREU COMERCIO DE PRODUTOS AGRI</t>
+  </si>
+  <si>
+    <t>1010003547</t>
+  </si>
+  <si>
+    <t>20.05.19 C+ NBPT</t>
+  </si>
+  <si>
+    <t>Leonardo Gomes Sampaio</t>
+  </si>
+  <si>
+    <t>GEY5J43</t>
+  </si>
+  <si>
+    <t>2149297</t>
+  </si>
+  <si>
+    <t>283803</t>
+  </si>
+  <si>
+    <t>1233241</t>
+  </si>
+  <si>
+    <t>80599183</t>
+  </si>
+  <si>
+    <t>2155409</t>
+  </si>
+  <si>
+    <t>283966</t>
+  </si>
+  <si>
+    <t>1233243</t>
+  </si>
+  <si>
+    <t>80599193</t>
+  </si>
+  <si>
+    <t>VASSULER COMERCIO DE ADUBO E CAFE L</t>
+  </si>
+  <si>
+    <t>1010003153</t>
+  </si>
+  <si>
+    <t>04.14.07 C+</t>
+  </si>
+  <si>
+    <t>GERALDO MAGELA SARNAGLIA</t>
+  </si>
+  <si>
+    <t>RNO7B17</t>
+  </si>
+  <si>
+    <t>2153575</t>
+  </si>
+  <si>
+    <t>284568</t>
+  </si>
+  <si>
+    <t>1233258</t>
+  </si>
+  <si>
+    <t>80599252</t>
+  </si>
+  <si>
+    <t>1010003644</t>
+  </si>
+  <si>
+    <t>06.30.06 C+</t>
+  </si>
+  <si>
+    <t>284569</t>
+  </si>
+  <si>
+    <t>1233262</t>
+  </si>
+  <si>
+    <t>80599251</t>
+  </si>
+  <si>
+    <t>CULTIVAR INSUMOS AGRICOLAS LTDA</t>
+  </si>
+  <si>
+    <t>PAULO MANSUR</t>
+  </si>
+  <si>
+    <t>IDT1626</t>
+  </si>
+  <si>
+    <t>2155615</t>
+  </si>
+  <si>
+    <t>283032</t>
+  </si>
+  <si>
+    <t>1233279</t>
+  </si>
+  <si>
+    <t>80599277</t>
+  </si>
+  <si>
+    <t>2153982</t>
+  </si>
+  <si>
+    <t>283035</t>
+  </si>
+  <si>
+    <t>1233300</t>
+  </si>
+  <si>
+    <t>80599276</t>
+  </si>
+  <si>
+    <t>2154579</t>
+  </si>
+  <si>
+    <t>283036</t>
+  </si>
+  <si>
+    <t>1233302</t>
+  </si>
+  <si>
+    <t>80599275</t>
   </si>
   <si>
     <t>CASA AGRI HELIO MORENO LTDA</t>
   </si>
   <si>
-    <t>1010002694</t>
-  </si>
-  <si>
-    <t>18.04.17 NBPT</t>
-  </si>
-  <si>
-    <t>EDIONIS FERREIRA DOS SANTOS</t>
-  </si>
-  <si>
-    <t>TOF6D10</t>
-  </si>
-  <si>
-    <t>2148423</t>
-  </si>
-  <si>
-    <t>282039</t>
-  </si>
-  <si>
-    <t>1230479</t>
-  </si>
-  <si>
-    <t>80593401</t>
-  </si>
-  <si>
-    <t>VINICIUS BURGARELLI COSTA</t>
-  </si>
-  <si>
-    <t>1010002488</t>
-  </si>
-  <si>
-    <t>26.00.26 BYSLB SEG</t>
-  </si>
-  <si>
-    <t>EDSON CESAR BARBOSA TRIVILIM</t>
-  </si>
-  <si>
-    <t>MPU6B44</t>
-  </si>
-  <si>
-    <t>2154035</t>
-  </si>
-  <si>
-    <t>280924</t>
-  </si>
-  <si>
-    <t>1230501</t>
-  </si>
-  <si>
-    <t>80593397</t>
-  </si>
-  <si>
-    <t>H2N ABREU COMERCIO DE PRODUTOS AGRI</t>
-  </si>
-  <si>
-    <t>1010001181</t>
-  </si>
-  <si>
-    <t>33.00.00 NBPT</t>
-  </si>
-  <si>
-    <t>ATILA CORREA</t>
-  </si>
-  <si>
-    <t>GKW0E90</t>
-  </si>
-  <si>
-    <t>2149297</t>
-  </si>
-  <si>
-    <t>280068</t>
-  </si>
-  <si>
-    <t>1230502</t>
-  </si>
-  <si>
-    <t>80593424</t>
-  </si>
-  <si>
-    <t>1010003557</t>
-  </si>
-  <si>
-    <t>18.04.17 C+ NBPT</t>
-  </si>
-  <si>
-    <t>RENATO RODRIGUES GONÇALVES</t>
-  </si>
-  <si>
-    <t>OCV3I73</t>
-  </si>
-  <si>
-    <t>2149295</t>
-  </si>
-  <si>
-    <t>280066</t>
-  </si>
-  <si>
-    <t>1230511</t>
-  </si>
-  <si>
-    <t>80593461</t>
-  </si>
-  <si>
-    <t>MP COMERCIAL AGRICOLA LTDA</t>
-  </si>
-  <si>
-    <t>1010003163</t>
-  </si>
-  <si>
-    <t>03.17.00 C+</t>
-  </si>
-  <si>
-    <t>ELIAS COELHO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>PPR9A77</t>
-  </si>
-  <si>
-    <t>2155239</t>
-  </si>
-  <si>
-    <t>282989</t>
-  </si>
-  <si>
-    <t>1230514</t>
-  </si>
-  <si>
-    <t>80593480</t>
+    <t>1010001346</t>
+  </si>
+  <si>
+    <t>20.10.10 NBPT</t>
+  </si>
+  <si>
+    <t>João Marcos Silveira vieira</t>
+  </si>
+  <si>
+    <t>SFT0C40</t>
+  </si>
+  <si>
+    <t>2156056</t>
+  </si>
+  <si>
+    <t>284280</t>
+  </si>
+  <si>
+    <t>1233307</t>
+  </si>
+  <si>
+    <t>80599320</t>
+  </si>
+  <si>
+    <t>284281</t>
+  </si>
+  <si>
+    <t>1233308</t>
+  </si>
+  <si>
+    <t>80599321</t>
+  </si>
+  <si>
+    <t>2151635</t>
+  </si>
+  <si>
+    <t>284170</t>
+  </si>
+  <si>
+    <t>1233310</t>
+  </si>
+  <si>
+    <t>80599322</t>
+  </si>
+  <si>
+    <t>9</t>
   </si>
   <si>
     <t>COOPERATIVA AGRARIA DOS CAFEICULTOR</t>
   </si>
   <si>
-    <t>1010002973</t>
-  </si>
-  <si>
-    <t>08.40.08+0,1B+0,2ZN C HMC</t>
-  </si>
-  <si>
-    <t>BIG BAG 1000KG</t>
-  </si>
-  <si>
-    <t>LUIZ ACERBI</t>
-  </si>
-  <si>
-    <t>JLX3480</t>
+    <t>FRANCISCO FERREIRA DA FONSECA NETTO</t>
+  </si>
+  <si>
+    <t>QRL3D08</t>
+  </si>
+  <si>
+    <t>2154199</t>
+  </si>
+  <si>
+    <t>282599</t>
+  </si>
+  <si>
+    <t>1233172</t>
+  </si>
+  <si>
+    <t>80599134</t>
+  </si>
+  <si>
+    <t>1010001404</t>
+  </si>
+  <si>
+    <t>20.00.20 NBPT</t>
+  </si>
+  <si>
+    <t>VALDECY PEREIRA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>MQC3I82</t>
+  </si>
+  <si>
+    <t>284210</t>
+  </si>
+  <si>
+    <t>1233174</t>
+  </si>
+  <si>
+    <t>80599137</t>
+  </si>
+  <si>
+    <t>1233175</t>
+  </si>
+  <si>
+    <t>80599138</t>
+  </si>
+  <si>
+    <t>284223</t>
+  </si>
+  <si>
+    <t>1233176</t>
+  </si>
+  <si>
+    <t>80599136</t>
+  </si>
+  <si>
+    <t>SERGIO GANHO</t>
+  </si>
+  <si>
+    <t>RBF3B48</t>
   </si>
   <si>
     <t>2154198</t>
   </si>
   <si>
-    <t>283010</t>
-  </si>
-  <si>
-    <t>1230555</t>
-  </si>
-  <si>
-    <t>80593527</t>
-  </si>
-  <si>
-    <t>1010000036</t>
-  </si>
-  <si>
-    <t>MAP 11-52-00</t>
-  </si>
-  <si>
-    <t>FABIO DE SOUZA CRUZ</t>
-  </si>
-  <si>
-    <t>LXA8250</t>
-  </si>
-  <si>
-    <t>2154486</t>
-  </si>
-  <si>
-    <t>282855</t>
-  </si>
-  <si>
-    <t>1230577</t>
-  </si>
-  <si>
-    <t>80593597</t>
-  </si>
-  <si>
-    <t>CULTIVAR INSUMOS AGRICOLAS LTDA</t>
-  </si>
-  <si>
-    <t>WALACE MARTINELLI</t>
-  </si>
-  <si>
-    <t>KSR6C49</t>
-  </si>
-  <si>
-    <t>2153982</t>
-  </si>
-  <si>
-    <t>279307</t>
-  </si>
-  <si>
-    <t>1230579</t>
-  </si>
-  <si>
-    <t>80593588</t>
-  </si>
-  <si>
-    <t>ROGERIO DINIZ DA SILVA</t>
-  </si>
-  <si>
-    <t>MSQ9I16</t>
-  </si>
-  <si>
-    <t>281299</t>
-  </si>
-  <si>
-    <t>1230600</t>
-  </si>
-  <si>
-    <t>80593591</t>
-  </si>
-  <si>
-    <t>281350</t>
-  </si>
-  <si>
-    <t>1230602</t>
-  </si>
-  <si>
-    <t>80593593</t>
-  </si>
-  <si>
-    <t>283019</t>
-  </si>
-  <si>
-    <t>1230603</t>
-  </si>
-  <si>
-    <t>80593594</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>1010001068</t>
-  </si>
-  <si>
-    <t>KCL 00-00-61 SLB</t>
-  </si>
-  <si>
-    <t>SACARIA 25KG</t>
-  </si>
-  <si>
-    <t>2154303</t>
-  </si>
-  <si>
-    <t>281876</t>
+    <t>283013</t>
+  </si>
+  <si>
+    <t>1233190</t>
+  </si>
+  <si>
+    <t>80599167</t>
+  </si>
+  <si>
+    <t>1010001005</t>
+  </si>
+  <si>
+    <t>MC 19-04-19+1MG+2S+0,2B+0,1ZN FRV</t>
+  </si>
+  <si>
+    <t>LACI RODRIGUES DE SOUZA</t>
+  </si>
+  <si>
+    <t>RQR6F86</t>
+  </si>
+  <si>
+    <t>2154666</t>
+  </si>
+  <si>
+    <t>284246</t>
+  </si>
+  <si>
+    <t>1233253</t>
+  </si>
+  <si>
+    <t>80599242</t>
   </si>
   <si>
     <t/>
-  </si>
-  <si>
-    <t>80593459</t>
-  </si>
-  <si>
-    <t>282891</t>
-  </si>
-  <si>
-    <t>80593460</t>
-  </si>
-  <si>
-    <t>JOAO MARCOS SILVEIRA VIEIRA</t>
-  </si>
-  <si>
-    <t>SFT0C40</t>
-  </si>
-  <si>
-    <t>2151650</t>
-  </si>
-  <si>
-    <t>282044</t>
-  </si>
-  <si>
-    <t>80593479</t>
   </si>
   <si>
     <t>Planta</t>
@@ -528,7 +702,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="8" customWidth="1"/>
@@ -538,10 +712,10 @@
     <col min="5" max="5" bestFit="1" width="17" customWidth="1"/>
     <col min="6" max="6" bestFit="1" width="37" customWidth="1"/>
     <col min="7" max="7" bestFit="1" width="20" customWidth="1"/>
-    <col min="8" max="8" bestFit="1" width="27" customWidth="1"/>
+    <col min="8" max="8" bestFit="1" width="35" customWidth="1"/>
     <col min="9" max="9" bestFit="1" width="20" customWidth="1"/>
     <col min="10" max="10" bestFit="1" width="18" customWidth="1"/>
-    <col min="11" max="11" bestFit="1" width="31" customWidth="1"/>
+    <col min="11" max="11" bestFit="1" width="37" customWidth="1"/>
     <col min="12" max="12" bestFit="1" width="9" customWidth="1"/>
     <col min="13" max="13" bestFit="1" width="5" customWidth="1"/>
     <col min="14" max="14" bestFit="1" width="17" customWidth="1"/>
@@ -553,58 +727,58 @@
   <sheetData>
     <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>171</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>114</v>
+        <v>172</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>117</v>
+        <v>175</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>118</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>119</v>
+        <v>177</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>120</v>
+        <v>178</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>122</v>
+        <v>180</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>123</v>
+        <v>181</v>
       </c>
       <c r="L1" s="9" t="s">
-        <v>124</v>
+        <v>182</v>
       </c>
       <c r="M1" s="9" t="s">
-        <v>125</v>
+        <v>183</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>126</v>
+        <v>184</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>127</v>
+        <v>185</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>128</v>
+        <v>186</v>
       </c>
       <c r="Q1" s="9" t="s">
-        <v>129</v>
+        <v>187</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>130</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:18">
@@ -618,10 +792,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="2">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="E2" s="3">
-        <v>0.32697916666667</v>
+        <v>0.34456018518519</v>
       </c>
       <c r="F2" t="s">
         <v>3</v>
@@ -636,7 +810,7 @@
         <v>6</v>
       </c>
       <c r="J2" s="4">
-        <v>32.000</v>
+        <v>7.000</v>
       </c>
       <c r="K2" t="s">
         <v>7</v>
@@ -648,7 +822,7 @@
         <v>9</v>
       </c>
       <c r="N2" s="4">
-        <v>32.000</v>
+        <v>7.000</v>
       </c>
       <c r="O2" t="s">
         <v>10</v>
@@ -674,49 +848,49 @@
         <v>2</v>
       </c>
       <c r="D3" s="2">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="E3" s="3">
-        <v>0.32853009259259</v>
+        <v>0.34490740740741</v>
       </c>
       <c r="F3" t="s">
         <v>3</v>
       </c>
       <c r="G3" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J3" s="4">
-        <v>19.000</v>
+        <v>7.000</v>
       </c>
       <c r="K3" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L3" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M3" t="s">
         <v>9</v>
       </c>
       <c r="N3" s="4">
-        <v>19.000</v>
+        <v>7.000</v>
       </c>
       <c r="O3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="P3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="Q3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="R3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -730,49 +904,49 @@
         <v>2</v>
       </c>
       <c r="D4" s="2">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="E4" s="3">
-        <v>0.33020833333333</v>
+        <v>0.35473379629630</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="H4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I4" t="s">
         <v>6</v>
       </c>
       <c r="J4" s="4">
-        <v>19.000</v>
+        <v>8.000</v>
       </c>
       <c r="K4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="M4" t="s">
         <v>9</v>
       </c>
       <c r="N4" s="4">
-        <v>19.000</v>
+        <v>8.000</v>
       </c>
       <c r="O4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="P4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="Q4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="R4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -786,37 +960,37 @@
         <v>2</v>
       </c>
       <c r="D5" s="2">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="E5" s="3">
-        <v>0.33174768518519</v>
+        <v>0.35600694444444</v>
       </c>
       <c r="F5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I5" t="s">
         <v>6</v>
       </c>
       <c r="J5" s="4">
-        <v>32.000</v>
+        <v>3.000</v>
       </c>
       <c r="K5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="L5" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="M5" t="s">
         <v>9</v>
       </c>
       <c r="N5" s="4">
-        <v>32.000</v>
+        <v>3.000</v>
       </c>
       <c r="O5" t="s">
         <v>32</v>
@@ -842,49 +1016,49 @@
         <v>2</v>
       </c>
       <c r="D6" s="2">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="E6" s="3">
-        <v>0.33276620370370</v>
+        <v>0.35704861111111</v>
       </c>
       <c r="F6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G6" t="s">
         <v>36</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>37</v>
-      </c>
-      <c r="H6" t="s">
-        <v>38</v>
       </c>
       <c r="I6" t="s">
         <v>6</v>
       </c>
       <c r="J6" s="4">
-        <v>15.000</v>
+        <v>28.000</v>
       </c>
       <c r="K6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" t="s">
+        <v>9</v>
+      </c>
+      <c r="N6" s="4">
+        <v>28.000</v>
+      </c>
+      <c r="O6" t="s">
+        <v>26</v>
+      </c>
+      <c r="P6" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q6" t="s">
         <v>39</v>
       </c>
-      <c r="L6" t="s">
+      <c r="R6" t="s">
         <v>40</v>
-      </c>
-      <c r="M6" t="s">
-        <v>9</v>
-      </c>
-      <c r="N6" s="4">
-        <v>15.000</v>
-      </c>
-      <c r="O6" t="s">
-        <v>41</v>
-      </c>
-      <c r="P6" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>43</v>
-      </c>
-      <c r="R6" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -898,49 +1072,49 @@
         <v>2</v>
       </c>
       <c r="D7" s="2">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="E7" s="3">
-        <v>0.35784722222222</v>
+        <v>0.36214120370370</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G7" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="I7" t="s">
         <v>6</v>
       </c>
       <c r="J7" s="4">
-        <v>12.000</v>
+        <v>5.000</v>
       </c>
       <c r="K7" t="s">
+        <v>42</v>
+      </c>
+      <c r="L7" t="s">
+        <v>43</v>
+      </c>
+      <c r="M7" t="s">
+        <v>9</v>
+      </c>
+      <c r="N7" s="4">
+        <v>5.000</v>
+      </c>
+      <c r="O7" t="s">
+        <v>44</v>
+      </c>
+      <c r="P7" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>46</v>
+      </c>
+      <c r="R7" t="s">
         <v>47</v>
-      </c>
-      <c r="L7" t="s">
-        <v>48</v>
-      </c>
-      <c r="M7" t="s">
-        <v>9</v>
-      </c>
-      <c r="N7" s="4">
-        <v>12.000</v>
-      </c>
-      <c r="O7" t="s">
-        <v>49</v>
-      </c>
-      <c r="P7" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>51</v>
-      </c>
-      <c r="R7" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -954,19 +1128,19 @@
         <v>2</v>
       </c>
       <c r="D8" s="2">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="E8" s="3">
-        <v>0.36076388888889</v>
+        <v>0.36365740740741</v>
       </c>
       <c r="F8" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="G8" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>55</v>
+        <v>15</v>
       </c>
       <c r="I8" t="s">
         <v>6</v>
@@ -975,10 +1149,10 @@
         <v>14.000</v>
       </c>
       <c r="K8" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="L8" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="M8" t="s">
         <v>9</v>
@@ -987,16 +1161,16 @@
         <v>14.000</v>
       </c>
       <c r="O8" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="P8" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="Q8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="R8" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -1010,49 +1184,49 @@
         <v>2</v>
       </c>
       <c r="D9" s="2">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="E9" s="3">
-        <v>0.38931712962963</v>
+        <v>0.36511574074074</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="G9" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
       <c r="I9" t="s">
-        <v>65</v>
+        <v>6</v>
       </c>
       <c r="J9" s="4">
-        <v>26.000</v>
+        <v>7.000</v>
       </c>
       <c r="K9" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="L9" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="M9" t="s">
         <v>9</v>
       </c>
       <c r="N9" s="4">
-        <v>26.000</v>
+        <v>7.000</v>
       </c>
       <c r="O9" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="P9" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="Q9" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="R9" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -1066,49 +1240,49 @@
         <v>2</v>
       </c>
       <c r="D10" s="2">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="E10" s="3">
-        <v>0.41789351851852</v>
+        <v>0.36734953703704</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="G10" t="s">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="H10" t="s">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="I10" t="s">
         <v>6</v>
       </c>
       <c r="J10" s="4">
-        <v>16.000</v>
+        <v>7.000</v>
       </c>
       <c r="K10" t="s">
-        <v>74</v>
+        <v>53</v>
       </c>
       <c r="L10" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="M10" t="s">
         <v>9</v>
       </c>
       <c r="N10" s="4">
-        <v>16.000</v>
+        <v>7.000</v>
       </c>
       <c r="O10" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="P10" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="Q10" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="R10" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -1122,49 +1296,49 @@
         <v>2</v>
       </c>
       <c r="D11" s="2">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="E11" s="3">
-        <v>0.42024305555556</v>
+        <v>0.36856481481481</v>
       </c>
       <c r="F11" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="G11" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="H11" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="I11" t="s">
         <v>6</v>
       </c>
       <c r="J11" s="4">
-        <v>15.000</v>
+        <v>14.000</v>
       </c>
       <c r="K11" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="L11" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="M11" t="s">
         <v>9</v>
       </c>
       <c r="N11" s="4">
-        <v>15.000</v>
+        <v>14.000</v>
       </c>
       <c r="O11" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="P11" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="Q11" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="R11" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -1178,49 +1352,49 @@
         <v>2</v>
       </c>
       <c r="D12" s="2">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="E12" s="3">
-        <v>0.42111111111111</v>
+        <v>0.37069444444444</v>
       </c>
       <c r="F12" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="G12" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H12" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="I12" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J12" s="4">
-        <v>6.000</v>
+        <v>18.000</v>
       </c>
       <c r="K12" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="L12" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="M12" t="s">
         <v>9</v>
       </c>
       <c r="N12" s="4">
-        <v>6.000</v>
+        <v>18.000</v>
       </c>
       <c r="O12" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="P12" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="Q12" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="R12" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:18">
@@ -1234,49 +1408,49 @@
         <v>2</v>
       </c>
       <c r="D13" s="2">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="E13" s="3">
-        <v>0.42248842592593</v>
+        <v>0.37194444444444</v>
       </c>
       <c r="F13" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s">
-        <v>19</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="I13" t="s">
         <v>6</v>
       </c>
       <c r="J13" s="4">
-        <v>5.000</v>
+        <v>40.000</v>
       </c>
       <c r="K13" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="L13" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="M13" t="s">
         <v>9</v>
       </c>
       <c r="N13" s="4">
-        <v>5.000</v>
+        <v>40.000</v>
       </c>
       <c r="O13" t="s">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="P13" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="Q13" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="R13" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -1290,49 +1464,49 @@
         <v>2</v>
       </c>
       <c r="D14" s="2">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="E14" s="3">
-        <v>0.42381944444444</v>
+        <v>0.37326388888889</v>
       </c>
       <c r="F14" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="G14" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="H14" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="I14" t="s">
         <v>6</v>
       </c>
       <c r="J14" s="4">
-        <v>8.000</v>
+        <v>14.000</v>
       </c>
       <c r="K14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L14" t="s">
+        <v>66</v>
+      </c>
+      <c r="M14" t="s">
+        <v>9</v>
+      </c>
+      <c r="N14" s="4">
+        <v>14.000</v>
+      </c>
+      <c r="O14" t="s">
         <v>87</v>
       </c>
-      <c r="L14" t="s">
+      <c r="P14" t="s">
         <v>88</v>
       </c>
-      <c r="M14" t="s">
-        <v>9</v>
-      </c>
-      <c r="N14" s="4">
-        <v>8.000</v>
-      </c>
-      <c r="O14" t="s">
-        <v>23</v>
-      </c>
-      <c r="P14" t="s">
-        <v>95</v>
-      </c>
       <c r="Q14" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="R14" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -1340,55 +1514,55 @@
         <v>0</v>
       </c>
       <c r="B15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="2">
+        <v>46247</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.39267361111111</v>
+      </c>
+      <c r="F15" t="s">
+        <v>91</v>
+      </c>
+      <c r="G15" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" t="s">
+        <v>6</v>
+      </c>
+      <c r="J15" s="4">
+        <v>5.000</v>
+      </c>
+      <c r="K15" t="s">
+        <v>94</v>
+      </c>
+      <c r="L15" t="s">
+        <v>95</v>
+      </c>
+      <c r="M15" t="s">
+        <v>9</v>
+      </c>
+      <c r="N15" s="4">
+        <v>5.000</v>
+      </c>
+      <c r="O15" t="s">
+        <v>96</v>
+      </c>
+      <c r="P15" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q15" t="s">
         <v>98</v>
       </c>
-      <c r="C15" t="s">
-        <v>2</v>
-      </c>
-      <c r="D15" s="2">
-        <v>46241</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0.36270833333333</v>
-      </c>
-      <c r="F15" t="s">
-        <v>36</v>
-      </c>
-      <c r="G15" t="s">
+      <c r="R15" t="s">
         <v>99</v>
-      </c>
-      <c r="H15" t="s">
-        <v>100</v>
-      </c>
-      <c r="I15" t="s">
-        <v>101</v>
-      </c>
-      <c r="J15" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="K15" t="s">
-        <v>47</v>
-      </c>
-      <c r="L15" t="s">
-        <v>48</v>
-      </c>
-      <c r="M15" t="s">
-        <v>9</v>
-      </c>
-      <c r="N15" s="4">
-        <v>0.000</v>
-      </c>
-      <c r="O15" t="s">
-        <v>102</v>
-      </c>
-      <c r="P15" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>104</v>
-      </c>
-      <c r="R15" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -1396,55 +1570,55 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="C16" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="2">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="E16" s="3">
-        <v>0.36471064814815</v>
+        <v>0.39473379629630</v>
       </c>
       <c r="F16" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="G16" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I16" t="s">
-        <v>101</v>
+        <v>6</v>
       </c>
       <c r="J16" s="4">
-        <v>0.000</v>
+        <v>27.000</v>
       </c>
       <c r="K16" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="L16" t="s">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="M16" t="s">
         <v>9</v>
       </c>
       <c r="N16" s="4">
-        <v>0.000</v>
+        <v>27.000</v>
       </c>
       <c r="O16" t="s">
+        <v>96</v>
+      </c>
+      <c r="P16" t="s">
         <v>102</v>
       </c>
-      <c r="P16" t="s">
-        <v>106</v>
-      </c>
       <c r="Q16" t="s">
+        <v>103</v>
+      </c>
+      <c r="R16" t="s">
         <v>104</v>
-      </c>
-      <c r="R16" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:18">
@@ -1452,107 +1626,723 @@
         <v>0</v>
       </c>
       <c r="B17" t="s">
-        <v>98</v>
+        <v>1</v>
       </c>
       <c r="C17" t="s">
         <v>2</v>
       </c>
       <c r="D17" s="2">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="E17" s="3">
-        <v>0.36662037037037</v>
+        <v>0.44563657407407</v>
       </c>
       <c r="F17" t="s">
-        <v>18</v>
+        <v>105</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="H17" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="I17" t="s">
-        <v>101</v>
+        <v>6</v>
       </c>
       <c r="J17" s="4">
+        <v>7.000</v>
+      </c>
+      <c r="K17" t="s">
+        <v>106</v>
+      </c>
+      <c r="L17" t="s">
+        <v>107</v>
+      </c>
+      <c r="M17" t="s">
+        <v>9</v>
+      </c>
+      <c r="N17" s="4">
+        <v>7.000</v>
+      </c>
+      <c r="O17" t="s">
+        <v>108</v>
+      </c>
+      <c r="P17" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>110</v>
+      </c>
+      <c r="R17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18">
+      <c r="A18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2">
+        <v>46247</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0.44769675925926</v>
+      </c>
+      <c r="F18" t="s">
+        <v>105</v>
+      </c>
+      <c r="G18" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" t="s">
+        <v>6</v>
+      </c>
+      <c r="J18" s="4">
+        <v>14.000</v>
+      </c>
+      <c r="K18" t="s">
+        <v>106</v>
+      </c>
+      <c r="L18" t="s">
+        <v>107</v>
+      </c>
+      <c r="M18" t="s">
+        <v>9</v>
+      </c>
+      <c r="N18" s="4">
+        <v>14.000</v>
+      </c>
+      <c r="O18" t="s">
+        <v>112</v>
+      </c>
+      <c r="P18" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>114</v>
+      </c>
+      <c r="R18" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="2">
+        <v>46247</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0.45112268518519</v>
+      </c>
+      <c r="F19" t="s">
+        <v>105</v>
+      </c>
+      <c r="G19" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" t="s">
+        <v>6</v>
+      </c>
+      <c r="J19" s="4">
+        <v>13.000</v>
+      </c>
+      <c r="K19" t="s">
+        <v>106</v>
+      </c>
+      <c r="L19" t="s">
+        <v>107</v>
+      </c>
+      <c r="M19" t="s">
+        <v>9</v>
+      </c>
+      <c r="N19" s="4">
+        <v>13.000</v>
+      </c>
+      <c r="O19" t="s">
+        <v>116</v>
+      </c>
+      <c r="P19" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>118</v>
+      </c>
+      <c r="R19" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="2">
+        <v>46247</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0.46435185185185</v>
+      </c>
+      <c r="F20" t="s">
+        <v>120</v>
+      </c>
+      <c r="G20" t="s">
+        <v>121</v>
+      </c>
+      <c r="H20" t="s">
+        <v>122</v>
+      </c>
+      <c r="I20" t="s">
+        <v>6</v>
+      </c>
+      <c r="J20" s="4">
+        <v>9.500</v>
+      </c>
+      <c r="K20" t="s">
+        <v>123</v>
+      </c>
+      <c r="L20" t="s">
+        <v>124</v>
+      </c>
+      <c r="M20" t="s">
+        <v>9</v>
+      </c>
+      <c r="N20" s="4">
+        <v>9.500</v>
+      </c>
+      <c r="O20" t="s">
+        <v>125</v>
+      </c>
+      <c r="P20" t="s">
+        <v>126</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>127</v>
+      </c>
+      <c r="R20" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18">
+      <c r="A21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="2">
+        <v>46247</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0.46562500000000</v>
+      </c>
+      <c r="F21" t="s">
+        <v>120</v>
+      </c>
+      <c r="G21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" t="s">
+        <v>6</v>
+      </c>
+      <c r="J21" s="4">
+        <v>5.500</v>
+      </c>
+      <c r="K21" t="s">
+        <v>123</v>
+      </c>
+      <c r="L21" t="s">
+        <v>124</v>
+      </c>
+      <c r="M21" t="s">
+        <v>9</v>
+      </c>
+      <c r="N21" s="4">
+        <v>5.500</v>
+      </c>
+      <c r="O21" t="s">
+        <v>125</v>
+      </c>
+      <c r="P21" t="s">
+        <v>129</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>130</v>
+      </c>
+      <c r="R21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18">
+      <c r="A22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2">
+        <v>46247</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0.46847222222222</v>
+      </c>
+      <c r="F22" t="s">
+        <v>120</v>
+      </c>
+      <c r="G22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="4">
+        <v>4.000</v>
+      </c>
+      <c r="K22" t="s">
+        <v>123</v>
+      </c>
+      <c r="L22" t="s">
+        <v>124</v>
+      </c>
+      <c r="M22" t="s">
+        <v>9</v>
+      </c>
+      <c r="N22" s="4">
+        <v>4.000</v>
+      </c>
+      <c r="O22" t="s">
+        <v>132</v>
+      </c>
+      <c r="P22" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>134</v>
+      </c>
+      <c r="R22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18">
+      <c r="A23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="2">
+        <v>46247</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0.32901620370370</v>
+      </c>
+      <c r="F23" t="s">
+        <v>137</v>
+      </c>
+      <c r="G23" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" t="s">
+        <v>6</v>
+      </c>
+      <c r="J23" s="4">
+        <v>32.000</v>
+      </c>
+      <c r="K23" t="s">
+        <v>138</v>
+      </c>
+      <c r="L23" t="s">
+        <v>139</v>
+      </c>
+      <c r="M23" t="s">
+        <v>9</v>
+      </c>
+      <c r="N23" s="4">
         <v>0.000</v>
       </c>
-      <c r="K17" t="s">
-        <v>108</v>
-      </c>
-      <c r="L17" t="s">
-        <v>109</v>
-      </c>
-      <c r="M17" t="s">
-        <v>9</v>
-      </c>
-      <c r="N17" s="4">
+      <c r="O23" t="s">
+        <v>140</v>
+      </c>
+      <c r="P23" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>142</v>
+      </c>
+      <c r="R23" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18">
+      <c r="A24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="2">
+        <v>46247</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0.33224537037037</v>
+      </c>
+      <c r="F24" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" t="s">
+        <v>144</v>
+      </c>
+      <c r="H24" t="s">
+        <v>145</v>
+      </c>
+      <c r="I24" t="s">
+        <v>6</v>
+      </c>
+      <c r="J24" s="4">
+        <v>4.000</v>
+      </c>
+      <c r="K24" t="s">
+        <v>146</v>
+      </c>
+      <c r="L24" t="s">
+        <v>147</v>
+      </c>
+      <c r="M24" t="s">
+        <v>9</v>
+      </c>
+      <c r="N24" s="4">
         <v>0.000</v>
       </c>
-      <c r="O17" t="s">
-        <v>110</v>
-      </c>
-      <c r="P17" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>104</v>
-      </c>
-      <c r="R17" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18">
-      <c r="A18" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="D18" s="6"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="H18" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="I18" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="J18" s="8">
-        <v>219.000</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="L18" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="N18" s="8">
-        <v>219.000</v>
-      </c>
-      <c r="O18" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="P18" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q18" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="R18" s="5" t="s">
-        <v>104</v>
+      <c r="O24" t="s">
+        <v>26</v>
+      </c>
+      <c r="P24" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18">
+      <c r="A25" t="s">
+        <v>0</v>
+      </c>
+      <c r="B25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="2">
+        <v>46247</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0.33334490740741</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" t="s">
+        <v>22</v>
+      </c>
+      <c r="H25" t="s">
+        <v>23</v>
+      </c>
+      <c r="I25" t="s">
+        <v>6</v>
+      </c>
+      <c r="J25" s="4">
+        <v>12.000</v>
+      </c>
+      <c r="K25" t="s">
+        <v>146</v>
+      </c>
+      <c r="L25" t="s">
+        <v>147</v>
+      </c>
+      <c r="M25" t="s">
+        <v>9</v>
+      </c>
+      <c r="N25" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="O25" t="s">
+        <v>26</v>
+      </c>
+      <c r="P25" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>151</v>
+      </c>
+      <c r="R25" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18">
+      <c r="A26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="2">
+        <v>46247</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0.33458333333333</v>
+      </c>
+      <c r="F26" t="s">
+        <v>21</v>
+      </c>
+      <c r="G26" t="s">
+        <v>4</v>
+      </c>
+      <c r="H26" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" t="s">
+        <v>6</v>
+      </c>
+      <c r="J26" s="4">
+        <v>3.000</v>
+      </c>
+      <c r="K26" t="s">
+        <v>146</v>
+      </c>
+      <c r="L26" t="s">
+        <v>147</v>
+      </c>
+      <c r="M26" t="s">
+        <v>9</v>
+      </c>
+      <c r="N26" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="O26" t="s">
+        <v>32</v>
+      </c>
+      <c r="P26" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>154</v>
+      </c>
+      <c r="R26" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="A27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>136</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="2">
+        <v>46247</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0.34817129629630</v>
+      </c>
+      <c r="F27" t="s">
+        <v>137</v>
+      </c>
+      <c r="G27" t="s">
+        <v>63</v>
+      </c>
+      <c r="H27" t="s">
+        <v>64</v>
+      </c>
+      <c r="I27" t="s">
+        <v>6</v>
+      </c>
+      <c r="J27" s="4">
+        <v>32.000</v>
+      </c>
+      <c r="K27" t="s">
+        <v>156</v>
+      </c>
+      <c r="L27" t="s">
+        <v>157</v>
+      </c>
+      <c r="M27" t="s">
+        <v>9</v>
+      </c>
+      <c r="N27" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="O27" t="s">
+        <v>158</v>
+      </c>
+      <c r="P27" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>160</v>
+      </c>
+      <c r="R27" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
+      <c r="A28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="2">
+        <v>46247</v>
+      </c>
+      <c r="E28" s="3">
+        <v>0.38482638888889</v>
+      </c>
+      <c r="F28" t="s">
+        <v>78</v>
+      </c>
+      <c r="G28" t="s">
+        <v>162</v>
+      </c>
+      <c r="H28" t="s">
+        <v>163</v>
+      </c>
+      <c r="I28" t="s">
+        <v>6</v>
+      </c>
+      <c r="J28" s="4">
+        <v>20.000</v>
+      </c>
+      <c r="K28" t="s">
+        <v>164</v>
+      </c>
+      <c r="L28" t="s">
+        <v>165</v>
+      </c>
+      <c r="M28" t="s">
+        <v>9</v>
+      </c>
+      <c r="N28" s="4">
+        <v>0.000</v>
+      </c>
+      <c r="O28" t="s">
+        <v>166</v>
+      </c>
+      <c r="P28" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>168</v>
+      </c>
+      <c r="R28" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18">
+      <c r="A29" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="D29" s="6"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="J29" s="8">
+        <v>360.000</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="N29" s="8">
+        <v>257.000</v>
+      </c>
+      <c r="O29" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="P29" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="Q29" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="R29" s="5" t="s">
+        <v>170</v>
       </c>
     </row>
   </sheetData>
